--- a/ru/downloads/data-excel/7.3.1.1.xlsx
+++ b/ru/downloads/data-excel/7.3.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F0E4A1-D751-4554-B00D-9E8187E59BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -179,11 +180,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,7 +372,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -379,26 +380,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -406,9 +404,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -427,17 +422,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -445,18 +434,12 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -466,24 +449,24 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Normal_GDP1" xfId="5"/>
+    <cellStyle name="Normal_GDP1" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 11" xfId="6"/>
-    <cellStyle name="Обычный 2" xfId="2"/>
-    <cellStyle name="Обычный 3" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="4"/>
-    <cellStyle name="Обычный 6" xfId="3"/>
+    <cellStyle name="Обычный 11" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -499,9 +482,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -539,9 +522,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -576,7 +559,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -611,7 +594,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -784,28 +767,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="34.85546875" style="11" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="11" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="3" width="34.85546875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="6" customFormat="1" ht="32.25" customHeight="1">
+    <row r="1" spans="1:21" s="6" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="6" customFormat="1" ht="14.25" customHeight="1">
+    <row r="2" spans="1:21" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
@@ -816,12 +799,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="6" customFormat="1" ht="15.75" thickBot="1">
+    <row r="3" spans="1:21" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
+      <c r="U3"/>
     </row>
-    <row r="4" spans="1:20" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+    <row r="4" spans="1:21" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -846,401 +830,416 @@
       <c r="H4" s="9">
         <v>2011</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>2012</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>2013</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>2014</v>
       </c>
       <c r="L4" s="9">
         <v>2015</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>2016</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <v>2017</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>2018</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="9">
         <v>2019</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="11">
         <v>2020</v>
       </c>
-      <c r="R4" s="13">
+      <c r="R4" s="11">
         <v>2021</v>
       </c>
-      <c r="S4" s="13">
+      <c r="S4" s="11">
         <v>2022</v>
       </c>
-      <c r="T4" s="13">
+      <c r="T4" s="11">
         <v>2023</v>
       </c>
+      <c r="U4" s="28">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" s="6" customFormat="1" ht="30" customHeight="1">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:21" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="19">
         <v>78.2</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="19">
         <v>54.3</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="19">
         <v>48.7</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="19">
         <v>45.5</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="20">
         <v>42</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="19">
         <v>35.299999999999997</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="19">
         <v>31.4</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="19">
         <v>26.1</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L5" s="19">
         <v>26.7</v>
       </c>
-      <c r="M5" s="24">
+      <c r="M5" s="20">
         <v>22</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="19">
         <v>25.3</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="19">
         <v>25.5</v>
       </c>
-      <c r="P5" s="23">
+      <c r="P5" s="19">
         <v>20.5</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="19">
         <v>20.5</v>
       </c>
-      <c r="R5" s="23">
+      <c r="R5" s="19">
         <v>17.899999999999999</v>
       </c>
-      <c r="S5" s="24">
+      <c r="S5" s="20">
         <v>13.5</v>
       </c>
-      <c r="T5" s="24">
+      <c r="T5" s="20">
         <v>10.548986676463752</v>
       </c>
+      <c r="U5" s="20">
+        <v>10.1</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" s="19" customFormat="1" ht="24">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:21" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="25">
+      <c r="D6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="21">
         <v>1.2</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="21">
         <v>1.4</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="21">
         <v>1.4</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O6" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="P6" s="25">
+      <c r="P6" s="21">
         <v>1</v>
       </c>
-      <c r="Q6" s="25">
+      <c r="Q6" s="21">
         <v>0.9</v>
       </c>
-      <c r="R6" s="25">
+      <c r="R6" s="21">
         <v>0.7</v>
       </c>
-      <c r="S6" s="28">
+      <c r="S6" s="23">
         <v>0.60838488325428985</v>
       </c>
-      <c r="T6" s="28">
+      <c r="T6" s="23">
         <v>0.52772216684397011</v>
       </c>
+      <c r="U6" s="23">
+        <v>0.59129138189030261</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" ht="20.25" customHeight="1">
-      <c r="A7" s="26" t="s">
+    <row r="7" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="26">
+      <c r="D7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="21">
         <v>44.5</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="21">
         <v>56.5</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="21">
         <v>83.6</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="21">
         <v>55.4</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="21">
         <v>37.700000000000003</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="21">
         <v>22.8</v>
       </c>
-      <c r="O7" s="26">
+      <c r="O7" s="21">
         <v>30.3</v>
       </c>
-      <c r="P7" s="26">
+      <c r="P7" s="21">
         <v>23.6</v>
       </c>
-      <c r="Q7" s="26">
+      <c r="Q7" s="21">
         <v>24.4</v>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="21">
         <v>10.6</v>
       </c>
-      <c r="S7" s="29">
+      <c r="S7" s="23">
         <v>9.7809425542123645</v>
       </c>
-      <c r="T7" s="29">
+      <c r="T7" s="23">
         <v>8.3132801458370658</v>
       </c>
+      <c r="U7" s="23">
+        <v>9.2249400285496783</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:21" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="27">
+      <c r="D8" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="22">
         <v>264.3</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="22">
         <v>282.60000000000002</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="22">
         <v>254.1</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="22">
         <v>201.4</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="22">
         <v>195.8</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="22">
         <v>174.5</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="22">
         <v>149.30000000000001</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="22">
         <v>149.5</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="22">
         <v>146.5</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="22">
         <v>142.19999999999999</v>
       </c>
-      <c r="S8" s="30">
+      <c r="S8" s="24">
         <v>125.75892934584627</v>
       </c>
-      <c r="T8" s="30">
+      <c r="T8" s="24">
         <v>118.53273752919056</v>
       </c>
+      <c r="U8" s="24">
+        <v>96.311357489498022</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" ht="45">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
     </row>
-    <row r="10" spans="1:20">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
     </row>
-    <row r="11" spans="1:20">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="26"/>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
     </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="26"/>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
     </row>
-    <row r="13" spans="1:20">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="26"/>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
